--- a/docs/pssgen_vpr_template.xlsx
+++ b/docs/pssgen_vpr_template.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -143,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -180,11 +185,38 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -223,6 +255,41 @@
         <name val="Arial"/>
         <sz val="10"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFAB40"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00D9D9D9"/>
@@ -592,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -608,8 +675,8 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -619,8 +686,8 @@
     <col width="35" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
     <col width="35" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
@@ -628,32 +695,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>GROUP A — REQUIREMENT IDENTITY  (pssgen import — do not edit)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>GROUP B — VERIFICATION PLANNING  (engineer)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>GROUP C — IMPLEMENTATION  (engineer)</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="S1" s="19" t="inlineStr">
         <is>
           <t>GROUP D — EXECUTION RESULTS  (pssgen)</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="AB1" s="20" t="inlineStr">
         <is>
           <t>GROUP E — CLOSURE  (engineer)</t>
         </is>
       </c>
-      <c r="AB1" s="6" t="inlineStr">
+      <c r="AF1" s="21" t="inlineStr">
         <is>
           <t>GROUP F — PROGRAM CONTEXT  (set once per release)</t>
         </is>
@@ -725,87 +792,107 @@
           <t>Risk_Acceptance</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="22" t="inlineStr">
+        <is>
+          <t>Verification_Category</t>
+        </is>
+      </c>
+      <c r="O2" s="22" t="inlineStr">
+        <is>
+          <t>Applicability</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Test_Name</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>HDL_Source</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Sim_Mode</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>RTL_Status</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>RTL_Run_Date</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>RTL_Commit</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>RTL_Evidence</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t>Gate_Status</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>Gate_Evidence</t>
         </is>
       </c>
-      <c r="W2" s="7" t="inlineStr">
+      <c r="Y2" s="22" t="inlineStr">
+        <is>
+          <t>Config_Set</t>
+        </is>
+      </c>
+      <c r="Z2" s="22" t="inlineStr">
+        <is>
+          <t>Tool_Version</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
         <is>
           <t>Anomaly_ID</t>
         </is>
       </c>
-      <c r="X2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>Overall_Status</t>
         </is>
       </c>
-      <c r="Y2" s="7" t="inlineStr">
+      <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>Closure_Author</t>
         </is>
       </c>
-      <c r="Z2" s="7" t="inlineStr">
+      <c r="AD2" s="7" t="inlineStr">
         <is>
           <t>Closure_Date</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AE2" s="7" t="inlineStr">
         <is>
           <t>Closure_Notes</t>
         </is>
       </c>
-      <c r="AB2" s="7" t="inlineStr">
+      <c r="AF2" s="7" t="inlineStr">
         <is>
           <t>IP_Version</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AG2" s="7" t="inlineStr">
         <is>
           <t>Target_Device</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AH2" s="7" t="inlineStr">
         <is>
           <t>Spec_Revision</t>
         </is>
@@ -877,94 +964,123 @@
           <t>(populate only when WAIVED)</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="O3" s="23" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>block_feature_test</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="Q3" s="9" t="inlineStr">
         <is>
           <t>vhdl/block.vhd</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>RTL</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>NOT_RUN</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="8" t="inlineStr"/>
+      <c r="V3" s="9" t="inlineStr"/>
+      <c r="W3" s="8" t="inlineStr">
         <is>
           <t>NOT_RUN</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr"/>
-      <c r="W3" s="8" t="inlineStr"/>
-      <c r="X3" s="8">
-        <f>IF(K3="WAIVED","WAIVED",IF(H3="","OPEN",IF(Q3="PASS",IF(Y3&lt;&gt;"","CLOSED","PASSING"),IF(Q3="FAIL","FAILING","COVERED"))))</f>
+      <c r="X3" s="9" t="inlineStr"/>
+      <c r="Y3" s="23" t="inlineStr">
+        <is>
+          <t>G_FIFO_DEPTH=16, G_DEFAULT_BAUD=115200, G_CLK_FREQ_HZ=100000000</t>
+        </is>
+      </c>
+      <c r="Z3" s="23" t="inlineStr">
+        <is>
+          <t>Vivado 2024.1 / Questa 23.2</t>
+        </is>
+      </c>
+      <c r="AA3" s="8" t="inlineStr"/>
+      <c r="AB3" s="24">
+        <f>IF(K3="WAIVED","WAIVED",IF(H3="","OPEN",IF(S3="BLOCKED","BLOCKED",IF(S3="FAIL","FAILING",IF(S3="PASS",IF(AA3&lt;&gt;"","AT_RISK",IF(AC3&lt;&gt;"","CLOSED","PASSING")),"COVERED")))))</f>
         <v/>
-      </c>
-      <c r="Y3" s="8" t="inlineStr"/>
-      <c r="Z3" s="8" t="inlineStr"/>
-      <c r="AA3" s="9" t="inlineStr"/>
-      <c r="AB3" s="8" t="inlineStr">
-        <is>
-          <t>0.0.0</t>
-        </is>
       </c>
       <c r="AC3" s="8" t="inlineStr"/>
       <c r="AD3" s="8" t="inlineStr"/>
+      <c r="AE3" s="9" t="inlineStr"/>
+      <c r="AF3" s="8" t="inlineStr">
+        <is>
+          <t>0.0.0</t>
+        </is>
+      </c>
+      <c r="AG3" s="8" t="inlineStr"/>
+      <c r="AH3" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="AF1:AH1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="G1:O1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="X1:AA1"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="S1:AA1"/>
+    <mergeCell ref="AB1:AE1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:AD2000">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$X4="CLOSED"</formula>
+  <conditionalFormatting sqref="A4:AH2000">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="0">
+      <formula>$AB4="CLOSED"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$X4="PASSING"</formula>
+    <cfRule type="expression" priority="2" dxfId="5" stopIfTrue="0">
+      <formula>$AB4="PASSING"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$X4="FAILING"</formula>
+    <cfRule type="expression" priority="3" dxfId="6" stopIfTrue="0">
+      <formula>$AB4="AT_RISK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>$X4="WAIVED"</formula>
+    <cfRule type="expression" priority="4" dxfId="7" stopIfTrue="0">
+      <formula>$AB4="FAILING"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="8" stopIfTrue="0">
+      <formula>$AB4="WAIVED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation sqref="C4:C2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Requirement Type" prompt="functional / structural / parametric / build-time / infrastructure" type="list">
+  <dataValidations count="9">
+    <dataValidation sqref="C4:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"functional,structural,parametric,build-time,infrastructure"</formula1>
     </dataValidation>
-    <dataValidation sqref="G4:G2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Verification Method" prompt="test / inspection / analysis / build-time" type="list">
+    <dataValidation sqref="G4:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"test,inspection,analysis,build-time"</formula1>
     </dataValidation>
-    <dataValidation sqref="K4:K2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Disposition" prompt="GENERATED = planned  CONFIRMED = evidence accepted  WAIVED = explicitly excluded" type="list">
+    <dataValidation sqref="K4:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"GENERATED,CONFIRMED,WAIVED"</formula1>
     </dataValidation>
-    <dataValidation sqref="M4:M2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Risk Acceptance" prompt="Required when Disposition = WAIVED. HIGH requires Closure_Author signature." type="list">
+    <dataValidation sqref="M4:M2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOW,MEDIUM,HIGH"</formula1>
     </dataValidation>
-    <dataValidation sqref="P4:P2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Simulation Mode" prompt="RTL / gate-level / formal" type="list">
-      <formula1>"RTL,gate-level,formal"</formula1>
+    <dataValidation sqref="N4:N2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Functional,Structural,Protocol_Compliance,Reset,CDC,Error_Handling,Parametric,Infrastructure"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q4:Q2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="RTL Status" prompt="PASS / FAIL / NOT_RUN / BLOCKED — written by pssgen" type="list">
+    <dataValidation sqref="O4:O2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ALL,PARITY_ENABLED,FIFO_DEPTH_GT_16,CONFIG_SPECIFIC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R4:R2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"RTL,gate-level,post-layout,HIL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S4:S2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,NOT_RUN,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation sqref="U4:U2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Gate Status" prompt="PASS / FAIL / NOT_RUN — written by pssgen after gate-level sim" type="list">
+    <dataValidation sqref="W4:W2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,NOT_RUN"</formula1>
     </dataValidation>
   </dataValidations>
@@ -979,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -989,16 +1105,10 @@
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>COVERAGE GOALS — one row per COV item</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" ht="18" customHeight="1"/>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -1035,7 +1145,12 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>Coverage_Type</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1043,11 +1158,14 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="G3:G500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="COV Status" prompt="PLANNED / IMPLEMENTED / PASSING / FAILING" type="list">
       <formula1>"PLANNED,IMPLEMENTED,PASSING,FAILING"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Functional,Code,Assertion,Toggle,FSM,Mixed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1240,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1253,15 +1371,11 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>ANOMALIES — defect records referenced by VPR Anomaly_ID</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" ht="18" customHeight="1"/>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -1311,20 +1425,36 @@
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Closed_Date</t>
+        </is>
+      </c>
+      <c r="K2" s="22" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>Regression_Fixed</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="D3:D500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Severity" prompt="CRITICAL / MAJOR / MINOR / OBSERVATION" type="list">
       <formula1>"CRITICAL,MAJOR,MINOR,OBSERVATION"</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="Status" prompt="OPEN / IN_PROGRESS / RESOLVED / CLOSED" type="list">
       <formula1>"OPEN,IN_PROGRESS,RESOLVED,CLOSED"</formula1>
     </dataValidation>
+    <dataValidation sqref="K3:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Functional,Timing,None"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"YES,NO,PENDING"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/pssgen_vpr_template.xlsx
+++ b/docs/pssgen_vpr_template.xlsx
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1155,6 +1155,168 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Seq_Status</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Stimulus_VSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/pssgen_vpr_template.xlsx
+++ b/docs/pssgen_vpr_template.xlsx
@@ -1095,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1165,6 +1165,16 @@
           <t>Stimulus_VSL</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>VSL_Notes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Seq_Review</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="J3" t="inlineStr">
@@ -1172,7 +1182,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="J4" t="inlineStr">
@@ -1180,7 +1195,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="J5" t="inlineStr">
@@ -1188,7 +1208,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="J6" t="inlineStr">
@@ -1196,7 +1221,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="J7" t="inlineStr">
@@ -1204,7 +1234,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="J8" t="inlineStr">
@@ -1212,7 +1247,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="J9" t="inlineStr">
@@ -1220,7 +1260,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="J10" t="inlineStr">
@@ -1228,7 +1273,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="J11" t="inlineStr">
@@ -1236,7 +1286,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="J12" t="inlineStr">
@@ -1244,7 +1299,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="J13" t="inlineStr">
@@ -1252,7 +1312,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="J14" t="inlineStr">
@@ -1260,7 +1325,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="J15" t="inlineStr">
@@ -1268,7 +1338,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="J16" t="inlineStr">
@@ -1276,7 +1351,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="J17" t="inlineStr">
@@ -1284,7 +1364,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="J18" t="inlineStr">
@@ -1292,7 +1377,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="J19" t="inlineStr">
@@ -1300,7 +1390,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="J20" t="inlineStr">
@@ -1308,7 +1403,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="J21" t="inlineStr">
@@ -1316,7 +1416,12 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/pssgen_vpr_template.xlsx
+++ b/docs/pssgen_vpr_template.xlsx
@@ -1182,7 +1182,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1195,7 +1194,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1208,7 +1206,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1221,7 +1218,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1234,7 +1230,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1247,7 +1242,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1260,7 +1254,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1273,7 +1266,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1286,7 +1278,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1299,7 +1290,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1312,7 +1302,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1325,7 +1314,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1338,7 +1326,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1351,7 +1338,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1364,7 +1350,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1377,7 +1362,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1390,7 +1374,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1403,7 +1386,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1416,7 +1398,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>DRAFT</t>
@@ -1427,12 +1408,18 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="G3:G500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list." promptTitle="COV Status" prompt="PLANNED / IMPLEMENTED / PASSING / FAILING" type="list">
       <formula1>"PLANNED,IMPLEMENTED,PASSING,FAILING"</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Functional,Code,Assertion,Toggle,FSM,Mixed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"DRAFT,REVIEWED,APPROVED"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"NONE,PHASE_1,PHASE_2_GAP"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
